--- a/2026/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
+++ b/2026/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5732819D-161C-4F5F-965E-8400F2BE34B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB583894-03A5-42F7-A7A6-05F09C0F77AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -26,12 +26,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="161">
   <si>
     <t>U.F.</t>
   </si>
@@ -267,9 +270,6 @@
     <t>DOMICILIO: MINISTRO BRIN 3219</t>
   </si>
   <si>
-    <t>SUTHER / FATHERY</t>
-  </si>
-  <si>
     <t>Gastos Legales</t>
   </si>
   <si>
@@ -394,6 +394,126 @@
   </si>
   <si>
     <t>Daniel Exner</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Noelia</t>
+  </si>
+  <si>
+    <t>Legales</t>
+  </si>
+  <si>
+    <t>Eliseo</t>
+  </si>
+  <si>
+    <t>HORAS EXTRAS FUMIGACION</t>
+  </si>
+  <si>
+    <t>3-SERVICIOS COMUNES</t>
+  </si>
+  <si>
+    <t>4- MANTENIMIENTO DE PARTES COMUNES</t>
+  </si>
+  <si>
+    <t>5- GASTO DE ADMINISTRACION</t>
+  </si>
+  <si>
+    <t>6-SEGUROS OBLIGATORIOS</t>
+  </si>
+  <si>
+    <t>7-GASTOS LEGALES</t>
+  </si>
+  <si>
+    <t>INTERES por MORA 3,7%</t>
+  </si>
+  <si>
+    <t>Horas extra fumigacion</t>
+  </si>
+  <si>
+    <t>ARCA NO SE PAGA HASTA RESOLVER LA SITUACION CUENTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sueldo Sra Monica Forment </t>
+  </si>
+  <si>
+    <t>AYSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romera Carlos Augusto </t>
+  </si>
+  <si>
+    <t>REEMPLAZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascensor </t>
+  </si>
+  <si>
+    <t>Ordinarios:</t>
+  </si>
+  <si>
+    <t>Le queda a favor esto actualmente</t>
+  </si>
+  <si>
+    <t>INGRESO</t>
+  </si>
+  <si>
+    <t>Ingreso por alquiler Piso 6 UF 24 y Expensas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso por pago de Expensas </t>
+  </si>
+  <si>
+    <t>Extraordinarias</t>
+  </si>
+  <si>
+    <t>Reemplazo por vacaciones</t>
+  </si>
+  <si>
+    <t>Seguro - Reemplazo</t>
+  </si>
+  <si>
+    <t>Acuerdo de deuda - Sindicatos</t>
+  </si>
+  <si>
+    <t>subidos en jul10</t>
+  </si>
+  <si>
+    <t>VTO: 17/9</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - AGOSTO</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - AGOSTO</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Cambio de transformador 220volts a A24 volts</t>
+  </si>
+  <si>
+    <t>Colcoacion de termotanque - Materiales + Mano de obra</t>
+  </si>
+  <si>
+    <t>Cuota 5 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Cambio de cañeria de entrada</t>
+  </si>
+  <si>
+    <t>Ezequiel Sarro Murillo -  Sr. Abogado - Presentacion de escrito</t>
+  </si>
+  <si>
+    <t>Cetrogar - Compra de termotanque escorial multigas Col 45L</t>
+  </si>
+  <si>
+    <t>Sr. Andres Jose - Electricista - Campio de termica - Materiales + mano de obra</t>
+  </si>
+  <si>
+    <t>SINDICATOS - SUTHER, FATHERY, SERACARH</t>
   </si>
   <si>
     <r>
@@ -403,123 +523,13 @@
       <rPr>
         <b/>
         <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>SUELDO ENCARGADA</t>
     </r>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>Noelia</t>
-  </si>
-  <si>
-    <t>Legales</t>
-  </si>
-  <si>
-    <t>Eliseo</t>
-  </si>
-  <si>
-    <t>HORAS EXTRAS FUMIGACION</t>
-  </si>
-  <si>
-    <t>3-SERVICIOS COMUNES</t>
-  </si>
-  <si>
-    <t>4- MANTENIMIENTO DE PARTES COMUNES</t>
-  </si>
-  <si>
-    <t>5- GASTO DE ADMINISTRACION</t>
-  </si>
-  <si>
-    <t>6-SEGUROS OBLIGATORIOS</t>
-  </si>
-  <si>
-    <t>7-GASTOS LEGALES</t>
-  </si>
-  <si>
-    <t>INTERES por MORA 3,7%</t>
-  </si>
-  <si>
-    <t>Horas extra fumigacion</t>
-  </si>
-  <si>
-    <t>ARCA NO SE PAGA HASTA RESOLVER LA SITUACION CUENTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sueldo Sra Monica Forment </t>
-  </si>
-  <si>
-    <t>AYSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romera Carlos Augusto </t>
-  </si>
-  <si>
-    <t>REEMPLAZO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascensor </t>
-  </si>
-  <si>
-    <t>Ordinarios:</t>
-  </si>
-  <si>
-    <t>Le queda a favor esto actualmente</t>
-  </si>
-  <si>
-    <t>INGRESO</t>
-  </si>
-  <si>
-    <t>Ingreso por alquiler Piso 6 UF 24 y Expensas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingreso por pago de Expensas </t>
-  </si>
-  <si>
-    <t>Extraordinarias</t>
-  </si>
-  <si>
-    <t>Reemplazo por vacaciones</t>
-  </si>
-  <si>
-    <t>Seguro - Reemplazo</t>
-  </si>
-  <si>
-    <t>Acuerdo de deuda - Sindicatos</t>
-  </si>
-  <si>
-    <t>subidos en jul10</t>
-  </si>
-  <si>
-    <t>VTO: 17/9</t>
-  </si>
-  <si>
-    <t>AGOSTO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - AGOSTO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - AGOSTO</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de transformador 220volts a A24 volts</t>
-  </si>
-  <si>
-    <t>Colcoacion de termotanque - Materiales + Mano de obra</t>
-  </si>
-  <si>
-    <t>Cuota 5 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de cañeria de entrada</t>
-  </si>
-  <si>
-    <t>Cetrigar - Compra de termotanque escorial multigas Col 45L</t>
   </si>
 </sst>
 </file>
@@ -536,7 +546,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,11 +647,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF444746"/>
-      <name val="Google Sans"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -704,13 +709,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -722,21 +720,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -751,6 +736,27 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1335,7 +1341,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1347,9 +1353,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1427,53 +1430,38 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="8" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1484,102 +1472,79 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1587,55 +1552,54 @@
     <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1645,127 +1609,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1780,10 +1630,10 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1795,8 +1645,165 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2244,19 +2251,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="8"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2266,1265 +2273,1538 @@
       <c r="G1" s="3"/>
       <c r="H1" s="9"/>
     </row>
-    <row r="2" spans="1:9" ht="48" customHeight="1">
+    <row r="2" spans="1:11" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="205"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="D3" s="14" t="s">
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="144"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="207">
+      <c r="E3" s="166">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="208"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="10"/>
-      <c r="D4" s="14" t="s">
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="164"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="168" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="10"/>
-      <c r="D5" s="14" t="s">
+      <c r="F4" s="165"/>
+      <c r="G4" s="165"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="164"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="170">
         <v>30707328890</v>
       </c>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="10"/>
-      <c r="D6" s="14" t="s">
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="164"/>
+      <c r="B6" s="165"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="10"/>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
-      <c r="A8" s="18" t="s">
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="169"/>
+      <c r="I6" s="165"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="164"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="165"/>
+    </row>
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="18.75">
+      <c r="A8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="89" t="s">
-        <v>151</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="15" t="s">
+      <c r="F8" s="75" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="171"/>
+      <c r="B9" s="172"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="172"/>
+      <c r="G9" s="172"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="B10" s="165"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="E11" s="14"/>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="215"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="216"/>
-    </row>
-    <row r="13" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="217" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="217"/>
-      <c r="G14" s="217"/>
-      <c r="H14" s="217"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="172" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="73">
-        <v>400043.91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="172" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="137"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="73">
-        <v>-63006.91</v>
-      </c>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="172" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="73">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="172" t="s">
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="165"/>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A11" s="12"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="165"/>
+      <c r="K11" s="165"/>
+    </row>
+    <row r="12" spans="1:11" ht="67.5" hidden="1" customHeight="1">
+      <c r="A12" s="145"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="146"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
+    </row>
+    <row r="13" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A13" s="174"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="165"/>
+      <c r="K13" s="165"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75">
+      <c r="A14" s="177" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="177"/>
+      <c r="C14" s="177"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="177"/>
+      <c r="F14" s="177"/>
+      <c r="G14" s="177"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="165"/>
+      <c r="J14" s="165"/>
+      <c r="K14" s="165"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="178" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="179"/>
+      <c r="C15" s="179"/>
+      <c r="D15" s="179"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="110">
+        <v>433458.65</v>
+      </c>
+      <c r="I15" s="165"/>
+      <c r="J15" s="165"/>
+      <c r="K15" s="165"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="178" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="179"/>
+      <c r="C16" s="179"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="110">
+        <v>-68269.649999999994</v>
+      </c>
+      <c r="I16" s="180"/>
+      <c r="J16" s="165"/>
+      <c r="K16" s="165"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="178" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="179"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="110">
+        <v>0</v>
+      </c>
+      <c r="I17" s="180"/>
+      <c r="J17" s="165"/>
+      <c r="K17" s="165"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="137"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="69">
+      <c r="B18" s="179"/>
+      <c r="C18" s="179"/>
+      <c r="D18" s="179"/>
+      <c r="E18" s="179"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="181">
         <f>SUM(H15:H17)</f>
-        <v>337037</v>
-      </c>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="214" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="214"/>
-      <c r="G19" s="214"/>
-      <c r="H19" s="214"/>
-    </row>
-    <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="172" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="137"/>
-      <c r="C20" s="137"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="172" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="137"/>
-      <c r="C21" s="137"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="172" t="s">
+        <v>365189</v>
+      </c>
+      <c r="I18" s="180"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
+    </row>
+    <row r="19" spans="1:11" hidden="1">
+      <c r="A19" s="182" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="182"/>
+      <c r="C19" s="182"/>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
+      <c r="F19" s="182"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="182"/>
+      <c r="I19" s="165"/>
+      <c r="J19" s="165"/>
+      <c r="K19" s="165"/>
+    </row>
+    <row r="20" spans="1:11" hidden="1">
+      <c r="A20" s="178" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="179"/>
+      <c r="C20" s="179"/>
+      <c r="D20" s="179"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="110">
+        <v>0</v>
+      </c>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
+    </row>
+    <row r="21" spans="1:11" hidden="1">
+      <c r="A21" s="178" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="179"/>
+      <c r="C21" s="179"/>
+      <c r="D21" s="179"/>
+      <c r="E21" s="179"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="179"/>
+      <c r="H21" s="110">
+        <v>0</v>
+      </c>
+      <c r="I21" s="165"/>
+      <c r="J21" s="165"/>
+      <c r="K21" s="165"/>
+    </row>
+    <row r="22" spans="1:11" hidden="1">
+      <c r="A22" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="137"/>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="69">
+      <c r="B22" s="179"/>
+      <c r="C22" s="179"/>
+      <c r="D22" s="179"/>
+      <c r="E22" s="179"/>
+      <c r="F22" s="179"/>
+      <c r="G22" s="179"/>
+      <c r="H22" s="181">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="213" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="213"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="213"/>
-      <c r="G23" s="213"/>
-      <c r="H23" s="213"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="137" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="137"/>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="137"/>
-      <c r="H24" s="73">
+      <c r="I22" s="165"/>
+      <c r="J22" s="165"/>
+      <c r="K22" s="165"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="183" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="183"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="165"/>
+      <c r="K23" s="165"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="179" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="179"/>
+      <c r="C24" s="179"/>
+      <c r="D24" s="179"/>
+      <c r="E24" s="179"/>
+      <c r="F24" s="179"/>
+      <c r="G24" s="179"/>
+      <c r="H24" s="110">
         <f>(17000+32000)/2</f>
         <v>24500</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="137"/>
-      <c r="B25" s="137"/>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="73"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="137" t="s">
+      <c r="I24" s="165"/>
+      <c r="J24" s="165"/>
+      <c r="K24" s="165"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="179"/>
+      <c r="B25" s="179"/>
+      <c r="C25" s="179"/>
+      <c r="D25" s="179"/>
+      <c r="E25" s="179"/>
+      <c r="F25" s="179"/>
+      <c r="G25" s="179"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="165"/>
+      <c r="K25" s="165"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="137"/>
-      <c r="C26" s="137"/>
-      <c r="D26" s="137"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="69">
+      <c r="B26" s="179"/>
+      <c r="C26" s="179"/>
+      <c r="D26" s="179"/>
+      <c r="E26" s="179"/>
+      <c r="F26" s="179"/>
+      <c r="G26" s="179"/>
+      <c r="H26" s="181">
         <f>SUM(H24:H25)</f>
         <v>24500</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="206" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="206"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="172"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="172" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="241">
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
+      <c r="K26" s="165"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="184" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="184"/>
+      <c r="C27" s="184"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="184"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="165"/>
+      <c r="K27" s="165"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="178"/>
+      <c r="B28" s="179"/>
+      <c r="C28" s="179"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="165"/>
+      <c r="J28" s="165"/>
+      <c r="K28" s="165"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="178" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="185"/>
+      <c r="C29" s="179"/>
+      <c r="D29" s="179"/>
+      <c r="E29" s="179"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="179"/>
+      <c r="H29" s="110">
         <f>18001.98+2000.22+31929.89</f>
         <v>51932.09</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="137" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="137"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="137" t="s">
+      <c r="I29" s="165"/>
+      <c r="J29" s="165"/>
+      <c r="K29" s="165"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="179" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="179"/>
+      <c r="C30" s="179"/>
+      <c r="D30" s="179"/>
+      <c r="E30" s="179"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="110">
+        <v>0</v>
+      </c>
+      <c r="I30" s="165"/>
+      <c r="J30" s="165"/>
+      <c r="K30" s="165"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="137"/>
-      <c r="C31" s="137"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="69">
+      <c r="B31" s="179"/>
+      <c r="C31" s="179"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="181">
         <f>SUM(H28:H30)</f>
         <v>51932.09</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="206" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="206"/>
-      <c r="C32" s="206"/>
-      <c r="D32" s="206"/>
-      <c r="E32" s="206"/>
-      <c r="F32" s="206"/>
-      <c r="G32" s="206"/>
-      <c r="H32" s="206"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A33" s="137" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="137"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="241">
+      <c r="I31" s="165"/>
+      <c r="J31" s="165"/>
+      <c r="K31" s="165"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="184" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="184"/>
+      <c r="C32" s="184"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="165"/>
+      <c r="K32" s="165"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A33" s="179" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="179"/>
+      <c r="C33" s="179"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="110">
         <v>283260.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="174" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="137"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="241">
+      <c r="I33" s="165"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="165"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="179"/>
+      <c r="C34" s="179"/>
+      <c r="D34" s="179"/>
+      <c r="E34" s="179"/>
+      <c r="F34" s="179"/>
+      <c r="G34" s="179"/>
+      <c r="H34" s="110">
         <v>81399.570000000007</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="137" t="s">
+      <c r="I34" s="165"/>
+      <c r="J34" s="165"/>
+      <c r="K34" s="165"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="175">
+      <c r="B35" s="179"/>
+      <c r="C35" s="179"/>
+      <c r="D35" s="179"/>
+      <c r="E35" s="179"/>
+      <c r="F35" s="179"/>
+      <c r="G35" s="179"/>
+      <c r="H35" s="187">
         <f>SUM(H33:H34)</f>
         <v>364660.07</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="217" t="s">
-        <v>128</v>
-      </c>
-      <c r="B36" s="217"/>
-      <c r="C36" s="217"/>
-      <c r="D36" s="217"/>
-      <c r="E36" s="217"/>
-      <c r="F36" s="217"/>
-      <c r="G36" s="217"/>
-      <c r="H36" s="217"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="80" t="s">
+      <c r="I35" s="165"/>
+      <c r="J35" s="165"/>
+      <c r="K35" s="165"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="177" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="177"/>
+      <c r="C36" s="177"/>
+      <c r="D36" s="177"/>
+      <c r="E36" s="177"/>
+      <c r="F36" s="177"/>
+      <c r="G36" s="177"/>
+      <c r="H36" s="177"/>
+      <c r="I36" s="165"/>
+      <c r="J36" s="165"/>
+      <c r="K36" s="165"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="137"/>
-      <c r="C37" s="137"/>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="137"/>
-      <c r="G37" s="137"/>
-      <c r="H37" s="241">
+      <c r="B37" s="179"/>
+      <c r="C37" s="179"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="110">
         <v>102500</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="137" t="s">
+      <c r="I37" s="165"/>
+      <c r="J37" s="165"/>
+      <c r="K37" s="165"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="179" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="137"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="137"/>
-      <c r="G38" s="137"/>
-      <c r="H38" s="241">
+      <c r="B38" s="179"/>
+      <c r="C38" s="179"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="110">
         <v>35247.839999999997</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="81" t="s">
+      <c r="I38" s="165"/>
+      <c r="J38" s="165"/>
+      <c r="K38" s="165"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="189" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="190"/>
+      <c r="C39" s="190"/>
+      <c r="D39" s="190"/>
+      <c r="E39" s="190"/>
+      <c r="F39" s="190"/>
+      <c r="G39" s="191"/>
+      <c r="H39" s="110">
+        <v>85000</v>
+      </c>
+      <c r="I39" s="165"/>
+      <c r="J39" s="165"/>
+      <c r="K39" s="165"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="189" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="190"/>
+      <c r="C40" s="190"/>
+      <c r="D40" s="190"/>
+      <c r="E40" s="190"/>
+      <c r="F40" s="190"/>
+      <c r="G40" s="191"/>
+      <c r="H40" s="110">
+        <v>250000</v>
+      </c>
+      <c r="I40" s="165"/>
+      <c r="J40" s="165"/>
+      <c r="K40" s="165"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="189" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="190"/>
+      <c r="C41" s="190"/>
+      <c r="D41" s="190"/>
+      <c r="E41" s="190"/>
+      <c r="F41" s="190"/>
+      <c r="G41" s="191"/>
+      <c r="H41" s="110">
+        <v>207000</v>
+      </c>
+      <c r="I41" s="165"/>
+      <c r="J41" s="165"/>
+      <c r="K41" s="165"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="189" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="190"/>
+      <c r="C42" s="190"/>
+      <c r="D42" s="190"/>
+      <c r="E42" s="190"/>
+      <c r="F42" s="190"/>
+      <c r="G42" s="191"/>
+      <c r="H42" s="110">
+        <v>355999</v>
+      </c>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="165"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="192" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" s="190"/>
+      <c r="C43" s="190"/>
+      <c r="D43" s="190"/>
+      <c r="E43" s="190"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="191"/>
+      <c r="H43" s="110">
+        <f>110000+12700</f>
+        <v>122700</v>
+      </c>
+      <c r="I43" s="165"/>
+      <c r="J43" s="165"/>
+      <c r="K43" s="165"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="179" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" s="179"/>
+      <c r="C44" s="179"/>
+      <c r="D44" s="179"/>
+      <c r="E44" s="179"/>
+      <c r="F44" s="179"/>
+      <c r="G44" s="179"/>
+      <c r="H44" s="110">
+        <v>75000</v>
+      </c>
+      <c r="I44" s="165"/>
+      <c r="J44" s="165"/>
+      <c r="K44" s="165"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="179" t="s">
         <v>154</v>
       </c>
-      <c r="B39" s="82"/>
-      <c r="C39" s="82"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="186"/>
-      <c r="H39" s="241">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="81" t="s">
-        <v>157</v>
-      </c>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="186"/>
-      <c r="H40" s="241">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="81" t="s">
-        <v>155</v>
-      </c>
-      <c r="B41" s="82"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="186"/>
-      <c r="H41" s="241">
-        <v>207000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="81" t="s">
-        <v>158</v>
-      </c>
-      <c r="B42" s="82"/>
-      <c r="C42" s="82"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="186"/>
-      <c r="H42" s="241">
-        <v>355999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="242"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="186"/>
-      <c r="H43" s="241">
-        <v>12700</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="137" t="s">
-        <v>152</v>
-      </c>
-      <c r="B44" s="137"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="241">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="137" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="137"/>
-      <c r="C45" s="137"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="137"/>
-      <c r="F45" s="137"/>
-      <c r="G45" s="137"/>
-      <c r="H45" s="241">
+      <c r="B45" s="179"/>
+      <c r="C45" s="179"/>
+      <c r="D45" s="179"/>
+      <c r="E45" s="179"/>
+      <c r="F45" s="179"/>
+      <c r="G45" s="179"/>
+      <c r="H45" s="110">
         <v>413700</v>
       </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="137" t="s">
+      <c r="I45" s="165"/>
+      <c r="J45" s="165"/>
+      <c r="K45" s="165"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="B46" s="137"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="69">
+      <c r="B46" s="179"/>
+      <c r="C46" s="179"/>
+      <c r="D46" s="179"/>
+      <c r="E46" s="179"/>
+      <c r="F46" s="179"/>
+      <c r="G46" s="179"/>
+      <c r="H46" s="181">
         <f>SUM(H37:H45)</f>
-        <v>1537146.8399999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="217" t="s">
-        <v>129</v>
-      </c>
-      <c r="B47" s="217"/>
-      <c r="C47" s="217"/>
-      <c r="D47" s="217"/>
-      <c r="E47" s="217"/>
-      <c r="F47" s="217"/>
-      <c r="G47" s="217"/>
-      <c r="H47" s="217"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="80" t="s">
+        <v>1647146.8399999999</v>
+      </c>
+      <c r="I46" s="165"/>
+      <c r="J46" s="165"/>
+      <c r="K46" s="165"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="177" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="177"/>
+      <c r="C47" s="177"/>
+      <c r="D47" s="177"/>
+      <c r="E47" s="177"/>
+      <c r="F47" s="177"/>
+      <c r="G47" s="177"/>
+      <c r="H47" s="177"/>
+      <c r="I47" s="165"/>
+      <c r="J47" s="165"/>
+      <c r="K47" s="165"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="73">
+      <c r="B48" s="188"/>
+      <c r="C48" s="188"/>
+      <c r="D48" s="188"/>
+      <c r="E48" s="188"/>
+      <c r="F48" s="188"/>
+      <c r="G48" s="188"/>
+      <c r="H48" s="110">
         <v>209000</v>
       </c>
-      <c r="J48" t="s">
-        <v>149</v>
-      </c>
+      <c r="I48" s="165"/>
+      <c r="J48" s="165" t="s">
+        <v>147</v>
+      </c>
+      <c r="K48" s="165"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="80" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="241">
+      <c r="A49" s="188" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="188"/>
+      <c r="C49" s="188"/>
+      <c r="D49" s="188"/>
+      <c r="E49" s="188"/>
+      <c r="F49" s="188"/>
+      <c r="G49" s="188"/>
+      <c r="H49" s="110">
         <v>50000</v>
       </c>
+      <c r="I49" s="165"/>
+      <c r="J49" s="165"/>
+      <c r="K49" s="165"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="137" t="s">
+      <c r="A50" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="137"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="137"/>
-      <c r="E50" s="137"/>
-      <c r="F50" s="137"/>
-      <c r="G50" s="137"/>
-      <c r="H50" s="175">
+      <c r="B50" s="179"/>
+      <c r="C50" s="179"/>
+      <c r="D50" s="179"/>
+      <c r="E50" s="179"/>
+      <c r="F50" s="179"/>
+      <c r="G50" s="179"/>
+      <c r="H50" s="187">
         <f>SUM(H48:H49)</f>
         <v>259000</v>
       </c>
-      <c r="K50" s="7"/>
+      <c r="I50" s="165"/>
+      <c r="J50" s="165"/>
+      <c r="K50" s="180"/>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="218" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="219"/>
-      <c r="C51" s="219"/>
-      <c r="D51" s="219"/>
-      <c r="E51" s="219"/>
-      <c r="F51" s="219"/>
-      <c r="G51" s="219"/>
-      <c r="H51" s="220"/>
+      <c r="A51" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="194"/>
+      <c r="C51" s="194"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="194"/>
+      <c r="G51" s="194"/>
+      <c r="H51" s="195"/>
+      <c r="I51" s="196"/>
+      <c r="J51" s="196"/>
+      <c r="K51" s="196"/>
     </row>
     <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="80"/>
-      <c r="C52" s="80"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="80"/>
-      <c r="F52" s="80"/>
-      <c r="G52" s="80"/>
-      <c r="H52" s="241">
+      <c r="A52" s="188" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="188"/>
+      <c r="C52" s="188"/>
+      <c r="D52" s="188"/>
+      <c r="E52" s="188"/>
+      <c r="F52" s="188"/>
+      <c r="G52" s="188"/>
+      <c r="H52" s="110">
         <v>28834</v>
       </c>
-      <c r="I52" s="60"/>
+      <c r="I52" s="197"/>
+      <c r="J52" s="196"/>
+      <c r="K52" s="196"/>
     </row>
     <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="80"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="69">
+      <c r="B53" s="188"/>
+      <c r="C53" s="188"/>
+      <c r="D53" s="188"/>
+      <c r="E53" s="188"/>
+      <c r="F53" s="188"/>
+      <c r="G53" s="188"/>
+      <c r="H53" s="181">
         <f>SUM(H52)</f>
         <v>28834</v>
       </c>
+      <c r="I53" s="196"/>
+      <c r="J53" s="196"/>
+      <c r="K53" s="196"/>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="217" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="217"/>
-      <c r="C54" s="217"/>
-      <c r="D54" s="217"/>
-      <c r="E54" s="217"/>
-      <c r="F54" s="217"/>
-      <c r="G54" s="217"/>
-      <c r="H54" s="217"/>
+      <c r="A54" s="177" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="177"/>
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
+      <c r="E54" s="177"/>
+      <c r="F54" s="177"/>
+      <c r="G54" s="177"/>
+      <c r="H54" s="177"/>
+      <c r="I54" s="196"/>
+      <c r="J54" s="196"/>
+      <c r="K54" s="196"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="80"/>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="73"/>
+      <c r="A55" s="188" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="188"/>
+      <c r="C55" s="188"/>
+      <c r="D55" s="188"/>
+      <c r="E55" s="188"/>
+      <c r="F55" s="188"/>
+      <c r="G55" s="188"/>
+      <c r="H55" s="110">
+        <v>110000</v>
+      </c>
+      <c r="I55" s="196"/>
+      <c r="J55" s="196"/>
+      <c r="K55" s="196"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A56" s="80" t="s">
+      <c r="A56" s="188" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="69">
+      <c r="B56" s="188"/>
+      <c r="C56" s="188"/>
+      <c r="D56" s="188"/>
+      <c r="E56" s="188"/>
+      <c r="F56" s="188"/>
+      <c r="G56" s="188"/>
+      <c r="H56" s="181">
         <f>SUM(H55:H55)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="60"/>
+        <v>110000</v>
+      </c>
+      <c r="I56" s="197"/>
+      <c r="J56" s="196"/>
+      <c r="K56" s="196"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="218"/>
-      <c r="B57" s="219"/>
-      <c r="C57" s="219"/>
-      <c r="D57" s="219"/>
-      <c r="E57" s="219"/>
-      <c r="F57" s="219"/>
-      <c r="G57" s="219"/>
-      <c r="H57" s="220"/>
+      <c r="A57" s="193"/>
+      <c r="B57" s="194"/>
+      <c r="C57" s="194"/>
+      <c r="D57" s="194"/>
+      <c r="E57" s="194"/>
+      <c r="F57" s="194"/>
+      <c r="G57" s="194"/>
+      <c r="H57" s="195"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A58" s="81"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="156">
-        <v>0</v>
-      </c>
+      <c r="A58" s="189"/>
+      <c r="B58" s="190"/>
+      <c r="C58" s="190"/>
+      <c r="D58" s="190"/>
+      <c r="E58" s="190"/>
+      <c r="F58" s="190"/>
+      <c r="G58" s="190"/>
+      <c r="H58" s="198">
+        <v>0</v>
+      </c>
+      <c r="I58" s="196"/>
+      <c r="J58" s="196"/>
+      <c r="K58" s="196"/>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A59" s="157"/>
-      <c r="B59" s="158"/>
-      <c r="C59" s="158"/>
-      <c r="D59" s="158"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="159">
-        <v>0</v>
-      </c>
+      <c r="A59" s="199"/>
+      <c r="B59" s="200"/>
+      <c r="C59" s="200"/>
+      <c r="D59" s="200"/>
+      <c r="E59" s="200"/>
+      <c r="F59" s="200"/>
+      <c r="G59" s="200"/>
+      <c r="H59" s="201">
+        <v>0</v>
+      </c>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="196"/>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A60" s="160"/>
-      <c r="B60" s="161"/>
-      <c r="C60" s="161"/>
-      <c r="D60" s="161"/>
-      <c r="E60" s="161"/>
-      <c r="F60" s="161"/>
-      <c r="G60" s="161"/>
-      <c r="H60" s="156">
+      <c r="A60" s="192"/>
+      <c r="B60" s="202"/>
+      <c r="C60" s="202"/>
+      <c r="D60" s="202"/>
+      <c r="E60" s="202"/>
+      <c r="F60" s="202"/>
+      <c r="G60" s="202"/>
+      <c r="H60" s="198">
         <f>H58+H59</f>
         <v>0</v>
       </c>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="196"/>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A61" s="221" t="s">
+      <c r="A61" s="203" t="s">
+        <v>79</v>
+      </c>
+      <c r="B61" s="204"/>
+      <c r="C61" s="204"/>
+      <c r="D61" s="204"/>
+      <c r="E61" s="204"/>
+      <c r="F61" s="204"/>
+      <c r="G61" s="204"/>
+      <c r="H61" s="205">
+        <f>H56</f>
+        <v>110000</v>
+      </c>
+      <c r="I61" s="196"/>
+      <c r="J61" s="196"/>
+      <c r="K61" s="196"/>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="206"/>
+      <c r="B62" s="206"/>
+      <c r="C62" s="206"/>
+      <c r="D62" s="206"/>
+      <c r="E62" s="206"/>
+      <c r="F62" s="206"/>
+      <c r="G62" s="206"/>
+      <c r="H62" s="206"/>
+      <c r="I62" s="196"/>
+      <c r="J62" s="196"/>
+      <c r="K62" s="196"/>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A63" s="207"/>
+      <c r="B63" s="207"/>
+      <c r="C63" s="207"/>
+      <c r="D63" s="207"/>
+      <c r="E63" s="207"/>
+      <c r="F63" s="207"/>
+      <c r="G63" s="207"/>
+      <c r="H63" s="207"/>
+      <c r="I63" s="196"/>
+      <c r="J63" s="196"/>
+      <c r="K63" s="196"/>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="208" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="208"/>
+      <c r="C64" s="208"/>
+      <c r="D64" s="208"/>
+      <c r="E64" s="208"/>
+      <c r="F64" s="208"/>
+      <c r="G64" s="208"/>
+      <c r="H64" s="209"/>
+      <c r="I64" s="196"/>
+      <c r="J64" s="196"/>
+      <c r="K64" s="196"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A65" s="210" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="211"/>
+      <c r="C65" s="211"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="211"/>
+      <c r="F65" s="211"/>
+      <c r="G65" s="212"/>
+      <c r="H65" s="110">
+        <f>67896.29+809224.86+120072.2</f>
+        <v>997193.35</v>
+      </c>
+      <c r="I65" s="196"/>
+      <c r="J65" s="196"/>
+      <c r="K65" s="196"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1">
+      <c r="A66" s="213" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="188"/>
+      <c r="C66" s="188"/>
+      <c r="D66" s="188"/>
+      <c r="E66" s="188"/>
+      <c r="F66" s="188"/>
+      <c r="G66" s="188"/>
+      <c r="H66" s="181">
+        <f>SUM(H65)</f>
+        <v>997193.35</v>
+      </c>
+      <c r="I66" s="196"/>
+      <c r="J66" s="196"/>
+      <c r="K66" s="196"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A67" s="196"/>
+      <c r="B67" s="196"/>
+      <c r="C67" s="196"/>
+      <c r="D67" s="196"/>
+      <c r="E67" s="196"/>
+      <c r="F67" s="196"/>
+      <c r="G67" s="196"/>
+      <c r="H67" s="214"/>
+      <c r="I67" s="196"/>
+      <c r="J67" s="196"/>
+      <c r="K67" s="196"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A68" s="215" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="222"/>
-      <c r="C61" s="222"/>
-      <c r="D61" s="222"/>
-      <c r="E61" s="222"/>
-      <c r="F61" s="222"/>
-      <c r="G61" s="222"/>
-      <c r="H61" s="162">
-        <f>H56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="224"/>
-      <c r="B62" s="224"/>
-      <c r="C62" s="224"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="224"/>
-      <c r="F62" s="224"/>
-      <c r="G62" s="224"/>
-      <c r="H62" s="224"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A63" s="225"/>
-      <c r="B63" s="225"/>
-      <c r="C63" s="225"/>
-      <c r="D63" s="225"/>
-      <c r="E63" s="225"/>
-      <c r="F63" s="225"/>
-      <c r="G63" s="225"/>
-      <c r="H63" s="225"/>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="223" t="s">
+      <c r="B68" s="216"/>
+      <c r="C68" s="216"/>
+      <c r="D68" s="216"/>
+      <c r="E68" s="216"/>
+      <c r="F68" s="216"/>
+      <c r="G68" s="216"/>
+      <c r="H68" s="217">
+        <f>H66</f>
+        <v>997193.35</v>
+      </c>
+      <c r="I68" s="196"/>
+      <c r="J68" s="196"/>
+      <c r="K68" s="196"/>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="218" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" s="219"/>
+      <c r="C69" s="219"/>
+      <c r="D69" s="219"/>
+      <c r="E69" s="219"/>
+      <c r="F69" s="219"/>
+      <c r="G69" s="220"/>
+      <c r="H69" s="217">
+        <v>1500000</v>
+      </c>
+      <c r="I69" s="196"/>
+      <c r="J69" s="196"/>
+      <c r="K69" s="196"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="218" t="s">
+        <v>91</v>
+      </c>
+      <c r="B70" s="219"/>
+      <c r="C70" s="219"/>
+      <c r="D70" s="219"/>
+      <c r="E70" s="219"/>
+      <c r="F70" s="219"/>
+      <c r="G70" s="220"/>
+      <c r="H70" s="217"/>
+      <c r="I70" s="196"/>
+      <c r="J70" s="196"/>
+      <c r="K70" s="196"/>
+    </row>
+    <row r="71" spans="1:11" ht="18.75">
+      <c r="A71" s="215" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="216"/>
+      <c r="C71" s="216"/>
+      <c r="D71" s="216"/>
+      <c r="E71" s="216"/>
+      <c r="F71" s="216"/>
+      <c r="G71" s="216"/>
+      <c r="H71" s="217">
+        <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
+        <v>2741262</v>
+      </c>
+      <c r="I71" s="165"/>
+      <c r="J71" s="221"/>
+      <c r="K71" s="222"/>
+    </row>
+    <row r="72" spans="1:11" ht="18.75">
+      <c r="A72" s="223" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" s="224"/>
+      <c r="C72" s="224"/>
+      <c r="D72" s="224"/>
+      <c r="E72" s="224"/>
+      <c r="F72" s="224"/>
+      <c r="G72" s="225"/>
+      <c r="H72" s="226">
+        <f>H69+H71</f>
+        <v>4241262</v>
+      </c>
+      <c r="I72" s="111"/>
+      <c r="J72" s="227"/>
+      <c r="K72" s="227"/>
+    </row>
+    <row r="73" spans="1:11" ht="18.75">
+      <c r="A73" s="223" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="224"/>
+      <c r="C73" s="224"/>
+      <c r="D73" s="224"/>
+      <c r="E73" s="224"/>
+      <c r="F73" s="224"/>
+      <c r="G73" s="225"/>
+      <c r="H73" s="228">
+        <f>H70+H68</f>
+        <v>997193.35</v>
+      </c>
+      <c r="I73" s="165"/>
+      <c r="J73" s="222"/>
+      <c r="K73" s="165"/>
+    </row>
+    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A74" s="229" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="223"/>
-      <c r="C64" s="223"/>
-      <c r="D64" s="223"/>
-      <c r="E64" s="223"/>
-      <c r="F64" s="223"/>
-      <c r="G64" s="223"/>
-      <c r="H64" s="163"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A65" s="226" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" s="227"/>
-      <c r="C65" s="227"/>
-      <c r="D65" s="227"/>
-      <c r="E65" s="227"/>
-      <c r="F65" s="227"/>
-      <c r="G65" s="228"/>
-      <c r="H65" s="73">
-        <f>60583.82+96723.22+413203.1</f>
-        <v>570510.14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1">
-      <c r="A66" s="127" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="69">
-        <f>SUM(H65)</f>
-        <v>570510.14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="128"/>
-      <c r="B67" s="128"/>
-      <c r="C67" s="128"/>
-      <c r="D67" s="128"/>
-      <c r="E67" s="128"/>
-      <c r="F67" s="128"/>
-      <c r="G67" s="128"/>
-      <c r="H67" s="129"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="194" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="195"/>
-      <c r="C68" s="195"/>
-      <c r="D68" s="195"/>
-      <c r="E68" s="195"/>
-      <c r="F68" s="195"/>
-      <c r="G68" s="195"/>
-      <c r="H68" s="130">
-        <f>H66</f>
-        <v>570510.14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="210" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="211"/>
-      <c r="C69" s="211"/>
-      <c r="D69" s="211"/>
-      <c r="E69" s="211"/>
-      <c r="F69" s="211"/>
-      <c r="G69" s="212"/>
-      <c r="H69" s="130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="210" t="s">
-        <v>92</v>
-      </c>
-      <c r="B70" s="211"/>
-      <c r="C70" s="211"/>
-      <c r="D70" s="211"/>
-      <c r="E70" s="211"/>
-      <c r="F70" s="211"/>
-      <c r="G70" s="212"/>
-      <c r="H70" s="130"/>
-    </row>
-    <row r="71" spans="1:11" ht="18">
-      <c r="A71" s="194" t="s">
-        <v>88</v>
-      </c>
-      <c r="B71" s="195"/>
-      <c r="C71" s="195"/>
-      <c r="D71" s="195"/>
-      <c r="E71" s="195"/>
-      <c r="F71" s="195"/>
-      <c r="G71" s="195"/>
-      <c r="H71" s="130">
-        <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
-        <v>2603110</v>
-      </c>
-      <c r="J71" s="171"/>
-      <c r="K71" s="142"/>
-    </row>
-    <row r="72" spans="1:11" ht="18">
-      <c r="A72" s="200" t="s">
-        <v>119</v>
-      </c>
-      <c r="B72" s="201"/>
-      <c r="C72" s="201"/>
-      <c r="D72" s="201"/>
-      <c r="E72" s="201"/>
-      <c r="F72" s="201"/>
-      <c r="G72" s="202"/>
-      <c r="H72" s="131">
-        <f>H69+H71</f>
-        <v>2603110</v>
-      </c>
-      <c r="I72" s="126"/>
-      <c r="J72" s="209"/>
-      <c r="K72" s="209"/>
-    </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="200" t="s">
-        <v>93</v>
-      </c>
-      <c r="B73" s="201"/>
-      <c r="C73" s="201"/>
-      <c r="D73" s="201"/>
-      <c r="E73" s="201"/>
-      <c r="F73" s="201"/>
-      <c r="G73" s="202"/>
-      <c r="H73" s="132">
-        <f>H70+H68</f>
-        <v>570510.14</v>
-      </c>
-      <c r="J73" s="142"/>
-    </row>
-    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A74" s="198" t="s">
+      <c r="B74" s="230"/>
+      <c r="C74" s="230"/>
+      <c r="D74" s="230"/>
+      <c r="E74" s="230"/>
+      <c r="F74" s="230"/>
+      <c r="G74" s="230"/>
+      <c r="H74" s="231">
+        <f>H71+H68</f>
+        <v>3738455.35</v>
+      </c>
+      <c r="I74" s="165"/>
+      <c r="J74" s="180"/>
+      <c r="K74" s="165"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75" hidden="1">
+      <c r="A75" s="232" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="233"/>
+      <c r="C75" s="233"/>
+      <c r="D75" s="233"/>
+      <c r="E75" s="233"/>
+      <c r="F75" s="233"/>
+      <c r="G75" s="233"/>
+      <c r="H75" s="234">
+        <f>H60</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="165"/>
+      <c r="J75" s="180"/>
+      <c r="K75" s="165"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75" hidden="1">
+      <c r="A76" s="235"/>
+      <c r="B76" s="235"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="235"/>
+      <c r="E76" s="235"/>
+      <c r="F76" s="235"/>
+      <c r="G76" s="235"/>
+      <c r="H76" s="236"/>
+      <c r="I76" s="165"/>
+      <c r="J76" s="180"/>
+      <c r="K76" s="165"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75" hidden="1">
+      <c r="A77" s="235"/>
+      <c r="B77" s="235"/>
+      <c r="C77" s="235"/>
+      <c r="D77" s="235"/>
+      <c r="E77" s="235"/>
+      <c r="F77" s="235"/>
+      <c r="G77" s="235"/>
+      <c r="H77" s="236"/>
+      <c r="I77" s="165"/>
+      <c r="J77" s="180"/>
+      <c r="K77" s="165"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
+      <c r="A78" s="235"/>
+      <c r="B78" s="235"/>
+      <c r="C78" s="235"/>
+      <c r="D78" s="235"/>
+      <c r="E78" s="235"/>
+      <c r="F78" s="235"/>
+      <c r="G78" s="235"/>
+      <c r="H78" s="236"/>
+      <c r="I78" s="165"/>
+      <c r="J78" s="180"/>
+      <c r="K78" s="165"/>
+    </row>
+    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A79" s="179"/>
+      <c r="B79" s="179"/>
+      <c r="C79" s="179"/>
+      <c r="D79" s="179"/>
+      <c r="E79" s="179"/>
+      <c r="F79" s="179"/>
+      <c r="G79" s="179"/>
+      <c r="H79" s="179"/>
+      <c r="I79" s="165"/>
+      <c r="J79" s="165"/>
+      <c r="K79" s="165"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75">
+      <c r="A80" s="237" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="238"/>
+      <c r="C80" s="238"/>
+      <c r="D80" s="238"/>
+      <c r="E80" s="238"/>
+      <c r="F80" s="238"/>
+      <c r="G80" s="238"/>
+      <c r="H80" s="239"/>
+      <c r="I80" s="165"/>
+      <c r="J80" s="165"/>
+      <c r="K80" s="165"/>
+    </row>
+    <row r="81" spans="1:11" ht="18.75">
+      <c r="A81" s="240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="241"/>
+      <c r="C81" s="241"/>
+      <c r="D81" s="241"/>
+      <c r="E81" s="241"/>
+      <c r="F81" s="241"/>
+      <c r="G81" s="241"/>
+      <c r="H81" s="242">
+        <v>5631401.1872961279</v>
+      </c>
+      <c r="I81" s="165"/>
+      <c r="J81" s="165"/>
+      <c r="K81" s="165"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="189" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82" s="190"/>
+      <c r="C82" s="190"/>
+      <c r="D82" s="190"/>
+      <c r="E82" s="190"/>
+      <c r="F82" s="190"/>
+      <c r="G82" s="190"/>
+      <c r="H82" s="18">
+        <f>Planilla!G32</f>
+        <v>2157075.7076916099</v>
+      </c>
+      <c r="I82" s="165"/>
+      <c r="J82" s="165"/>
+      <c r="K82" s="165"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="174" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" s="175"/>
+      <c r="C83" s="175"/>
+      <c r="D83" s="175"/>
+      <c r="E83" s="175"/>
+      <c r="F83" s="175"/>
+      <c r="G83" s="175"/>
+      <c r="H83" s="14">
+        <f>-(H74)</f>
+        <v>-3738455.35</v>
+      </c>
+      <c r="I83" s="165"/>
+      <c r="J83" s="165"/>
+      <c r="K83" s="165"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="199"/>
-      <c r="C74" s="199"/>
-      <c r="D74" s="199"/>
-      <c r="E74" s="199"/>
-      <c r="F74" s="199"/>
-      <c r="G74" s="199"/>
-      <c r="H74" s="133">
-        <f>H71+H68</f>
-        <v>3173620.14</v>
-      </c>
-      <c r="J74" s="7"/>
-    </row>
-    <row r="75" spans="1:11" ht="18" hidden="1">
-      <c r="A75" s="196" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="197"/>
-      <c r="C75" s="197"/>
-      <c r="D75" s="197"/>
-      <c r="E75" s="197"/>
-      <c r="F75" s="197"/>
-      <c r="G75" s="197"/>
-      <c r="H75" s="134">
-        <f>H60</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="7"/>
-    </row>
-    <row r="76" spans="1:11" ht="18" hidden="1">
-      <c r="A76" s="135"/>
-      <c r="B76" s="135"/>
-      <c r="C76" s="135"/>
-      <c r="D76" s="135"/>
-      <c r="E76" s="135"/>
-      <c r="F76" s="135"/>
-      <c r="G76" s="135"/>
-      <c r="H76" s="136"/>
-      <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="135"/>
-      <c r="B77" s="135"/>
-      <c r="C77" s="135"/>
-      <c r="D77" s="135"/>
-      <c r="E77" s="135"/>
-      <c r="F77" s="135"/>
-      <c r="G77" s="135"/>
-      <c r="H77" s="136"/>
-      <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="18" hidden="1">
-      <c r="A78" s="135"/>
-      <c r="B78" s="135"/>
-      <c r="C78" s="135"/>
-      <c r="D78" s="135"/>
-      <c r="E78" s="135"/>
-      <c r="F78" s="135"/>
-      <c r="G78" s="135"/>
-      <c r="H78" s="136"/>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A79" s="137"/>
-      <c r="B79" s="137"/>
-      <c r="C79" s="137"/>
-      <c r="D79" s="137"/>
-      <c r="E79" s="137"/>
-      <c r="F79" s="137"/>
-      <c r="G79" s="137"/>
-      <c r="H79" s="137"/>
-    </row>
-    <row r="80" spans="1:11" ht="18">
-      <c r="A80" s="191" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80" s="192"/>
-      <c r="C80" s="192"/>
-      <c r="D80" s="192"/>
-      <c r="E80" s="192"/>
-      <c r="F80" s="192"/>
-      <c r="G80" s="192"/>
-      <c r="H80" s="193"/>
-    </row>
-    <row r="81" spans="1:11" ht="18">
-      <c r="A81" s="138" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="139"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="139"/>
-      <c r="H81" s="140">
-        <v>4229401.2367692199</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="81" t="s">
-        <v>144</v>
-      </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="141">
-        <f>Planilla!G32</f>
-        <v>3698920.7905269074</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="B83" s="79"/>
-      <c r="C83" s="79"/>
-      <c r="D83" s="79"/>
-      <c r="E83" s="79"/>
-      <c r="F83" s="79"/>
-      <c r="G83" s="79"/>
-      <c r="H83" s="179">
-        <f>-(H74)</f>
-        <v>-3173620.14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B84" s="79"/>
-      <c r="C84" s="79"/>
-      <c r="D84" s="79"/>
-      <c r="E84" s="79"/>
-      <c r="F84" s="79"/>
-      <c r="G84" s="79"/>
-      <c r="H84" s="179">
+      <c r="B84" s="175"/>
+      <c r="C84" s="175"/>
+      <c r="D84" s="175"/>
+      <c r="E84" s="175"/>
+      <c r="F84" s="175"/>
+      <c r="G84" s="175"/>
+      <c r="H84" s="14">
         <f>-H61</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="6"/>
+        <v>-110000</v>
+      </c>
+      <c r="I84" s="165"/>
+      <c r="J84" s="165"/>
+      <c r="K84" s="196"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="78" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="121">
+      <c r="A85" s="174" t="s">
+        <v>141</v>
+      </c>
+      <c r="B85" s="175"/>
+      <c r="C85" s="175"/>
+      <c r="D85" s="175"/>
+      <c r="E85" s="175"/>
+      <c r="F85" s="175"/>
+      <c r="G85" s="175"/>
+      <c r="H85" s="84">
         <f>217300-H86</f>
         <v>154086</v>
       </c>
-      <c r="J85" s="7"/>
+      <c r="I85" s="165"/>
+      <c r="J85" s="180"/>
+      <c r="K85" s="165"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="78" t="s">
+      <c r="A86" s="174" t="s">
         <v>71</v>
       </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="121">
+      <c r="B86" s="175"/>
+      <c r="C86" s="175"/>
+      <c r="D86" s="175"/>
+      <c r="E86" s="175"/>
+      <c r="F86" s="175"/>
+      <c r="G86" s="175"/>
+      <c r="H86" s="84">
         <v>63214</v>
       </c>
-      <c r="I86" s="142"/>
-      <c r="J86" s="7"/>
+      <c r="I86" s="222"/>
+      <c r="J86" s="180"/>
+      <c r="K86" s="165"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="174" t="s">
+        <v>116</v>
+      </c>
+      <c r="B87" s="243"/>
+      <c r="C87" s="175"/>
+      <c r="D87" s="175"/>
+      <c r="E87" s="175"/>
+      <c r="F87" s="175"/>
+      <c r="G87" s="175"/>
+      <c r="H87" s="84"/>
+      <c r="I87" s="165"/>
+      <c r="J87" s="165"/>
+      <c r="K87" s="165"/>
+    </row>
+    <row r="88" spans="1:11" ht="18.75">
+      <c r="A88" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="70">
+        <f>SUM(H81:H87)</f>
+        <v>4157321.5449877377</v>
+      </c>
+      <c r="I88" s="165"/>
+      <c r="J88" s="165"/>
+      <c r="K88" s="165"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="90" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A90" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="149"/>
+      <c r="C90" s="149"/>
+      <c r="D90" s="149"/>
+      <c r="E90" s="149"/>
+      <c r="F90" s="149"/>
+      <c r="G90" s="149"/>
+      <c r="H90" s="150"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75">
+      <c r="A91" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="73"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="73"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
+      <c r="G91" s="73"/>
+      <c r="H91" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="B87" s="83"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="98"/>
-    </row>
-    <row r="88" spans="1:11" ht="18">
-      <c r="A88" s="22" t="s">
+      <c r="B92" s="77"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="110"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="55"/>
+      <c r="B93" s="83"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="18"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="55"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="18"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="84">
-        <f>SUM(H81:H87)</f>
-        <v>4972001.8872961272</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="15" thickBot="1"/>
-    <row r="90" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A90" s="188" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="189"/>
-      <c r="C90" s="189"/>
-      <c r="D90" s="189"/>
-      <c r="E90" s="189"/>
-      <c r="F90" s="189"/>
-      <c r="G90" s="189"/>
-      <c r="H90" s="190"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.6">
-      <c r="A91" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="87"/>
-      <c r="C91" s="87"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="87"/>
-      <c r="H91" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" s="91"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="125"/>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="61"/>
-      <c r="B93" s="97"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="21"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="21"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B95" s="85"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
-      <c r="E95" s="85"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="86">
+      <c r="B95" s="71"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="71"/>
+      <c r="E95" s="71"/>
+      <c r="F95" s="71"/>
+      <c r="G95" s="71"/>
+      <c r="H95" s="72">
         <f>SUM(H91:H94)</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="187"/>
-      <c r="B98" s="187"/>
-      <c r="C98" s="187"/>
-      <c r="D98" s="187"/>
-      <c r="E98" s="187"/>
-      <c r="F98" s="187"/>
-      <c r="G98" s="187"/>
-      <c r="H98" s="187"/>
+      <c r="A98" s="146"/>
+      <c r="B98" s="146"/>
+      <c r="C98" s="146"/>
+      <c r="D98" s="146"/>
+      <c r="E98" s="146"/>
+      <c r="F98" s="146"/>
+      <c r="G98" s="146"/>
+      <c r="H98" s="146"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="187"/>
-      <c r="B99" s="187"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="187"/>
-      <c r="E99" s="187"/>
-      <c r="F99" s="187"/>
-      <c r="G99" s="187"/>
-      <c r="H99" s="187"/>
+      <c r="A99" s="146"/>
+      <c r="B99" s="146"/>
+      <c r="C99" s="146"/>
+      <c r="D99" s="146"/>
+      <c r="E99" s="146"/>
+      <c r="F99" s="146"/>
+      <c r="G99" s="146"/>
+      <c r="H99" s="146"/>
     </row>
     <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="187"/>
-      <c r="B100" s="187"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="187"/>
-      <c r="E100" s="187"/>
-      <c r="F100" s="187"/>
-      <c r="G100" s="187"/>
-      <c r="H100" s="187"/>
+      <c r="A100" s="146"/>
+      <c r="B100" s="146"/>
+      <c r="C100" s="146"/>
+      <c r="D100" s="146"/>
+      <c r="E100" s="146"/>
+      <c r="F100" s="146"/>
+      <c r="G100" s="146"/>
+      <c r="H100" s="146"/>
     </row>
     <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="187"/>
-      <c r="B101" s="187"/>
-      <c r="C101" s="187"/>
-      <c r="D101" s="187"/>
-      <c r="E101" s="187"/>
-      <c r="F101" s="187"/>
-      <c r="G101" s="187"/>
-      <c r="H101" s="187"/>
+      <c r="A101" s="146"/>
+      <c r="B101" s="146"/>
+      <c r="C101" s="146"/>
+      <c r="D101" s="146"/>
+      <c r="E101" s="146"/>
+      <c r="F101" s="146"/>
+      <c r="G101" s="146"/>
+      <c r="H101" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A62:H63"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A98:H101"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
@@ -3541,14 +3821,11 @@
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A98:H101"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A65:G65"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3559,1383 +3836,1385 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
-      <c r="A1" s="102"/>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="104" t="s">
+      <c r="A1" s="88"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="105" t="str">
+      <c r="F1" s="91" t="str">
         <f>RESUMEN!F8</f>
         <v>AGOSTO</v>
       </c>
-      <c r="G1" s="106"/>
-      <c r="H1" s="104" t="str">
+      <c r="G1" s="92"/>
+      <c r="H1" s="90" t="str">
         <f>RESUMEN!G8</f>
         <v>VTO: 17/9</v>
       </c>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="107"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="93"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="124">
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="109">
         <v>1934410.7</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="115"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="101">
-        <v>4081947.54</v>
-      </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="61" t="s">
+      <c r="A3" s="101"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="87">
+        <v>2741262</v>
+      </c>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="163">
+        <v>997193.35</v>
+      </c>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
     </row>
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="119" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="185">
+      <c r="A4" s="104"/>
+      <c r="B4" s="105" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="105" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="141">
         <f>278067+10000+9000-3000-520+225+12</f>
         <v>293784</v>
       </c>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="61" t="s">
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A5" s="120"/>
-      <c r="B5" s="230">
+      <c r="A5" s="106"/>
+      <c r="B5" s="152">
         <f>C2</f>
         <v>1934410.7</v>
       </c>
-      <c r="C5" s="230"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="236">
-        <v>0</v>
-      </c>
-      <c r="F5" s="237"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="158">
+        <v>110000</v>
+      </c>
+      <c r="F5" s="159"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A6" s="120"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="232" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" s="233"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
+      <c r="A6" s="106"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="155"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="154" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="155"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
-      <c r="A7" s="120"/>
-      <c r="B7" s="230"/>
-      <c r="C7" s="230"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="234">
-        <v>570510</v>
-      </c>
-      <c r="F7" s="235"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="114"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
-      <c r="K7" s="114"/>
-      <c r="L7" s="114"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
+      <c r="A7" s="106"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="156">
+        <f>F3</f>
+        <v>997193.35</v>
+      </c>
+      <c r="F7" s="157"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
     </row>
     <row r="8" spans="1:17" ht="53.25" customHeight="1" thickBot="1">
-      <c r="A8" s="108" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="109" t="s">
+      <c r="A8" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="110" t="s">
+      <c r="C8" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="111" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="109" t="s">
+      <c r="D8" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="112" t="s">
+      <c r="F8" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="112" t="s">
-        <v>142</v>
-      </c>
-      <c r="H8" s="112" t="s">
+      <c r="G8" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="112" t="s">
-        <v>132</v>
-      </c>
-      <c r="J8" s="112" t="s">
+      <c r="I8" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="123" t="s">
-        <v>124</v>
-      </c>
-      <c r="L8" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="109" t="s">
+      <c r="K8" s="108" t="s">
+        <v>122</v>
+      </c>
+      <c r="L8" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="109" t="s">
-        <v>139</v>
-      </c>
-      <c r="O8" s="113" t="s">
+      <c r="N8" s="95" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="99" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1">
-      <c r="A9" s="169">
+      <c r="A9" s="130">
         <v>1</v>
       </c>
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="166" t="s">
+      <c r="C9" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="166" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="167">
+      <c r="D9" s="127" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="128">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="F9" s="98">
-        <v>177426.13652999999</v>
-      </c>
-      <c r="G9" s="176"/>
-      <c r="H9" s="68">
+      <c r="F9" s="84">
+        <v>285440.19193161</v>
+      </c>
+      <c r="G9" s="133">
+        <f>F9</f>
+        <v>285440.19193161</v>
+      </c>
+      <c r="H9" s="62">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>177426.13652999999</v>
-      </c>
-      <c r="I9" s="68">
+        <v>0</v>
+      </c>
+      <c r="I9" s="62">
         <f>H9*3.7%</f>
-        <v>6564.7670516100006</v>
-      </c>
-      <c r="J9" s="68">
+        <v>0</v>
+      </c>
+      <c r="J9" s="62">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="68">
+      <c r="K9" s="62">
         <f>E$5*E9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="68">
+        <v>4455</v>
+      </c>
+      <c r="L9" s="62">
         <f>E$7*E9</f>
-        <v>23105.655000000002</v>
-      </c>
-      <c r="M9" s="168">
+        <v>40386.330674999997</v>
+      </c>
+      <c r="M9" s="129">
         <f>B$5*E9</f>
         <v>78343.633350000004</v>
       </c>
-      <c r="N9" s="168">
+      <c r="N9" s="129">
         <f>B$7*E9</f>
         <v>0</v>
       </c>
-      <c r="O9" s="183">
+      <c r="O9" s="139">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>285440.19193161</v>
+        <v>123184.96402499999</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
-      <c r="A10" s="51">
+      <c r="A10" s="48">
         <v>2</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="45">
+      <c r="D10" s="78"/>
+      <c r="E10" s="42">
         <v>6.4799999999999996E-2</v>
       </c>
-      <c r="F10" s="17">
-        <v>283881.81844799995</v>
-      </c>
-      <c r="G10" s="176">
+      <c r="F10" s="14">
+        <v>162318.86135999998</v>
+      </c>
+      <c r="G10" s="133">
         <f>F10</f>
-        <v>283881.81844799995</v>
-      </c>
-      <c r="H10" s="24">
+        <v>162318.86135999998</v>
+      </c>
+      <c r="H10" s="21">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="21">
         <f>H10*3.7%</f>
         <v>0</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="21">
         <f t="shared" ref="J10:J31" si="1">IF(G10&gt;F10,G10-F10,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="68">
+      <c r="K10" s="62">
         <f t="shared" ref="K10:K31" si="2">E$5*E10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="68">
+        <v>7128</v>
+      </c>
+      <c r="L10" s="62">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
-        <v>36969.047999999995</v>
-      </c>
-      <c r="M10" s="25">
+        <v>64618.129079999992</v>
+      </c>
+      <c r="M10" s="22">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
         <v>125349.81335999999</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="22">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
         <v>0</v>
       </c>
-      <c r="O10" s="183">
+      <c r="O10" s="139">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>162318.86135999998</v>
+        <v>197095.94243999996</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
-      <c r="A11" s="164">
+      <c r="A11" s="125">
         <v>3</v>
       </c>
-      <c r="B11" s="165" t="s">
+      <c r="B11" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="166" t="s">
+      <c r="C11" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="166" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="167">
+      <c r="D11" s="127" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="128">
         <v>4.82E-2</v>
       </c>
-      <c r="F11" s="98">
-        <v>211159.00693199999</v>
-      </c>
-      <c r="G11" s="176">
+      <c r="F11" s="84">
+        <v>120737.17774</v>
+      </c>
+      <c r="G11" s="133">
         <f>F11</f>
-        <v>211159.00693199999</v>
-      </c>
-      <c r="H11" s="68">
+        <v>120737.17774</v>
+      </c>
+      <c r="H11" s="62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="68">
+      <c r="I11" s="62">
         <f t="shared" ref="I11:I31" si="7">H11*3.7%</f>
         <v>0</v>
       </c>
-      <c r="J11" s="68">
+      <c r="J11" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="68">
+      <c r="K11" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="68">
+        <v>5302</v>
+      </c>
+      <c r="L11" s="62">
         <f t="shared" si="3"/>
-        <v>27498.581999999999</v>
-      </c>
-      <c r="M11" s="168">
+        <v>48064.719469999996</v>
+      </c>
+      <c r="M11" s="129">
         <f t="shared" si="4"/>
         <v>93238.595740000004</v>
       </c>
-      <c r="N11" s="168">
+      <c r="N11" s="129">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="183">
+      <c r="O11" s="139">
         <f t="shared" si="6"/>
-        <v>120737.17774</v>
-      </c>
-      <c r="P11" s="171"/>
+        <v>146605.31521</v>
+      </c>
+      <c r="P11" s="132"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
-      <c r="A12" s="143">
+      <c r="A12" s="112">
         <v>4</v>
       </c>
-      <c r="B12" s="155" t="s">
+      <c r="B12" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="153" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="153" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="154">
+      <c r="C12" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="122" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="123">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="147">
-        <v>5964462.7322450671</v>
-      </c>
-      <c r="G12" s="177"/>
-      <c r="H12" s="148">
+      <c r="F12" s="116">
+        <v>6319161.1107881349</v>
+      </c>
+      <c r="G12" s="134"/>
+      <c r="H12" s="117">
         <f t="shared" si="0"/>
-        <v>5964462.7322450671</v>
-      </c>
-      <c r="I12" s="148">
+        <v>6319161.1107881349</v>
+      </c>
+      <c r="I12" s="117">
         <f t="shared" si="7"/>
-        <v>220685.12109306752</v>
-      </c>
-      <c r="J12" s="148">
+        <v>233808.96109916101</v>
+      </c>
+      <c r="J12" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="148">
+      <c r="K12" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="148">
+        <v>5885</v>
+      </c>
+      <c r="L12" s="117">
         <f t="shared" si="3"/>
-        <v>30522.285</v>
-      </c>
-      <c r="M12" s="149">
+        <v>53349.844225000001</v>
+      </c>
+      <c r="M12" s="118">
         <f t="shared" si="4"/>
         <v>103490.97245</v>
       </c>
-      <c r="N12" s="149">
+      <c r="N12" s="118">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O12" s="184">
+      <c r="O12" s="140">
         <f t="shared" si="6"/>
-        <v>6319161.1107881349</v>
+        <v>6715695.8885622956</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
-      <c r="A13" s="51">
+      <c r="A13" s="48">
         <v>5</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="93" t="s">
+      <c r="C13" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="92"/>
-      <c r="E13" s="45">
+      <c r="D13" s="78"/>
+      <c r="E13" s="42">
         <v>3.85E-2</v>
       </c>
-      <c r="F13" s="17">
-        <v>168664.35200999997</v>
-      </c>
-      <c r="G13" s="176">
+      <c r="F13" s="14">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="G13" s="133">
         <f>F13</f>
-        <v>168664.35200999997</v>
-      </c>
-      <c r="H13" s="24">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="68">
+      <c r="K13" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="68">
+        <v>4235</v>
+      </c>
+      <c r="L13" s="62">
         <f t="shared" si="3"/>
-        <v>21964.634999999998</v>
-      </c>
-      <c r="M13" s="25">
+        <v>38391.943975000002</v>
+      </c>
+      <c r="M13" s="22">
         <f t="shared" si="4"/>
         <v>74474.811950000003</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O13" s="183">
+      <c r="O13" s="139">
         <f t="shared" si="6"/>
-        <v>96439.446949999998</v>
+        <v>117101.755925</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
-      <c r="A14" s="51">
+      <c r="A14" s="48">
         <v>6</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="45">
+      <c r="D14" s="78"/>
+      <c r="E14" s="42">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F14" s="17">
-        <v>157274.03213399998</v>
-      </c>
-      <c r="G14" s="176">
+      <c r="F14" s="14">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="G14" s="133">
         <f>F14</f>
-        <v>157274.03213399998</v>
-      </c>
-      <c r="H14" s="24">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="H14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="68">
+      <c r="K14" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="68">
+        <v>3949</v>
+      </c>
+      <c r="L14" s="62">
         <f t="shared" si="3"/>
-        <v>20481.309000000001</v>
-      </c>
-      <c r="M14" s="25">
+        <v>35799.241264999997</v>
+      </c>
+      <c r="M14" s="22">
         <f t="shared" si="4"/>
         <v>69445.344129999998</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="183">
+      <c r="O14" s="139">
         <f t="shared" si="6"/>
-        <v>89926.653129999992</v>
+        <v>109193.585395</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
-      <c r="A15" s="51">
+      <c r="A15" s="48">
         <v>7</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="45">
+      <c r="C15" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="42">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F15" s="17">
-        <v>181368.93956399997</v>
-      </c>
-      <c r="G15" s="176">
+      <c r="F15" s="14">
+        <v>103703.71698</v>
+      </c>
+      <c r="G15" s="133">
         <f>F15</f>
-        <v>181368.93956399997</v>
-      </c>
-      <c r="H15" s="24">
+        <v>103703.71698</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="68">
+      <c r="K15" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="68">
+        <v>4554</v>
+      </c>
+      <c r="L15" s="62">
         <f t="shared" si="3"/>
-        <v>23619.114000000001</v>
-      </c>
-      <c r="M15" s="25">
+        <v>41283.804689999997</v>
+      </c>
+      <c r="M15" s="22">
         <f t="shared" si="4"/>
         <v>80084.602979999996</v>
       </c>
-      <c r="N15" s="25">
-        <v>0</v>
-      </c>
-      <c r="O15" s="183">
+      <c r="N15" s="22">
+        <v>0</v>
+      </c>
+      <c r="O15" s="139">
         <f t="shared" si="6"/>
-        <v>103703.71698</v>
-      </c>
-      <c r="Q15" s="180"/>
+        <v>125922.40766999999</v>
+      </c>
+      <c r="Q15" s="136"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
-      <c r="A16" s="51">
+      <c r="A16" s="48">
         <v>8</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="92" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="45">
+      <c r="D16" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="42">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F16" s="17">
-        <v>234377.73590999999</v>
-      </c>
-      <c r="G16" s="176">
+      <c r="F16" s="14">
+        <v>134013.25745</v>
+      </c>
+      <c r="G16" s="133">
         <f>F16</f>
-        <v>234377.73590999999</v>
-      </c>
-      <c r="H16" s="24">
+        <v>134013.25745</v>
+      </c>
+      <c r="H16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="68">
+      <c r="K16" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="68">
+        <v>5885</v>
+      </c>
+      <c r="L16" s="62">
         <f t="shared" si="3"/>
-        <v>30522.285</v>
-      </c>
-      <c r="M16" s="25">
+        <v>53349.844225000001</v>
+      </c>
+      <c r="M16" s="22">
         <f t="shared" si="4"/>
         <v>103490.97245</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="139">
         <f t="shared" si="6"/>
-        <v>134013.25745</v>
-      </c>
-      <c r="Q16" s="180"/>
+        <v>162725.81667500001</v>
+      </c>
+      <c r="Q16" s="136"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1">
-      <c r="A17" s="51">
+      <c r="A17" s="48">
         <v>9</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="45">
+      <c r="D17" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="42">
         <v>3.85E-2</v>
       </c>
-      <c r="F17" s="17">
-        <v>418221.4838209076</v>
-      </c>
-      <c r="G17" s="176">
-        <f>F17</f>
-        <v>418221.4838209076</v>
-      </c>
-      <c r="H17" s="24">
+      <c r="F17" s="14">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="G17" s="133"/>
+      <c r="H17" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="24">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="I17" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="24">
+        <v>3568.2595371500006</v>
+      </c>
+      <c r="J17" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="68">
+      <c r="K17" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="68">
+        <v>4235</v>
+      </c>
+      <c r="L17" s="62">
         <f t="shared" si="3"/>
-        <v>21964.634999999998</v>
-      </c>
-      <c r="M17" s="25">
+        <v>38391.943975000002</v>
+      </c>
+      <c r="M17" s="22">
         <f t="shared" si="4"/>
         <v>74474.811950000003</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O17" s="183">
+      <c r="O17" s="139">
         <f t="shared" si="6"/>
-        <v>96439.446949999998</v>
-      </c>
-      <c r="Q17" s="180"/>
+        <v>217109.46241214999</v>
+      </c>
+      <c r="Q17" s="136"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1">
-      <c r="A18" s="164">
+      <c r="A18" s="125">
         <v>10</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167">
+      <c r="D18" s="127"/>
+      <c r="E18" s="128">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F18" s="98">
-        <v>-32805.866497089621</v>
-      </c>
-      <c r="G18" s="176">
-        <f>RESUMEN!H37+RESUMEN!H44+RESUMEN!H49</f>
-        <v>227500</v>
-      </c>
-      <c r="H18" s="68">
+      <c r="F18" s="84">
+        <v>-161079.21336708963</v>
+      </c>
+      <c r="G18" s="133"/>
+      <c r="H18" s="62">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="68">
+      <c r="I18" s="62">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J18" s="68">
+      <c r="J18" s="62">
         <f t="shared" si="1"/>
-        <v>260305.86649708962</v>
-      </c>
-      <c r="K18" s="68">
+        <v>161079.21336708963</v>
+      </c>
+      <c r="K18" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="68">
+        <v>3949</v>
+      </c>
+      <c r="L18" s="62">
         <f t="shared" si="3"/>
-        <v>20481.309000000001</v>
-      </c>
-      <c r="M18" s="168">
+        <v>35799.241264999997</v>
+      </c>
+      <c r="M18" s="129">
         <f t="shared" si="4"/>
         <v>69445.344129999998</v>
       </c>
-      <c r="N18" s="168">
+      <c r="N18" s="129">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O18" s="183">
+      <c r="O18" s="139">
         <f t="shared" si="6"/>
-        <v>-170379.21336708963</v>
-      </c>
-      <c r="Q18" s="180"/>
+        <v>-51885.627972089635</v>
+      </c>
+      <c r="Q18" s="136"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1">
-      <c r="A19" s="143">
+      <c r="A19" s="112">
         <v>11</v>
       </c>
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="151" t="s">
+      <c r="C19" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="153" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="154">
+      <c r="D19" s="122" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="123">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="147">
-        <v>4239238.3269483093</v>
-      </c>
-      <c r="G19" s="177"/>
-      <c r="H19" s="148">
+      <c r="F19" s="116">
+        <v>4499793.8620253969</v>
+      </c>
+      <c r="G19" s="134"/>
+      <c r="H19" s="117">
         <f t="shared" si="0"/>
-        <v>4239238.3269483093</v>
-      </c>
-      <c r="I19" s="148">
+        <v>4499793.8620253969</v>
+      </c>
+      <c r="I19" s="117">
         <f t="shared" si="7"/>
-        <v>156851.81809708747</v>
-      </c>
-      <c r="J19" s="148">
+        <v>166492.3728949397</v>
+      </c>
+      <c r="J19" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="148">
+      <c r="K19" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="148">
+        <v>4554</v>
+      </c>
+      <c r="L19" s="117">
         <f t="shared" si="3"/>
-        <v>23619.114000000001</v>
-      </c>
-      <c r="M19" s="149">
+        <v>41283.804689999997</v>
+      </c>
+      <c r="M19" s="118">
         <f t="shared" si="4"/>
         <v>80084.602979999996</v>
       </c>
-      <c r="N19" s="149">
+      <c r="N19" s="118">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="184">
+      <c r="O19" s="140">
         <f t="shared" si="6"/>
-        <v>4499793.8620253969</v>
-      </c>
-      <c r="Q19" s="180"/>
+        <v>4792208.6425903365</v>
+      </c>
+      <c r="Q19" s="136"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1">
-      <c r="A20" s="51">
+      <c r="A20" s="48">
         <v>12</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="46">
+      <c r="C20" s="86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="43">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F20" s="17">
-        <v>234377.73590999999</v>
-      </c>
-      <c r="G20" s="176">
+      <c r="F20" s="14">
+        <v>134013.25745</v>
+      </c>
+      <c r="G20" s="133">
         <f>F20</f>
-        <v>234377.73590999999</v>
-      </c>
-      <c r="H20" s="24">
+        <v>134013.25745</v>
+      </c>
+      <c r="H20" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="68">
+      <c r="K20" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="68">
+        <v>5885</v>
+      </c>
+      <c r="L20" s="62">
         <f t="shared" si="3"/>
-        <v>30522.285</v>
-      </c>
-      <c r="M20" s="25">
+        <v>53349.844225000001</v>
+      </c>
+      <c r="M20" s="22">
         <f t="shared" si="4"/>
         <v>103490.97245</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="183">
+      <c r="O20" s="139">
         <f t="shared" si="6"/>
-        <v>134013.25745</v>
-      </c>
-      <c r="Q20" s="180"/>
+        <v>162725.81667500001</v>
+      </c>
+      <c r="Q20" s="136"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
-      <c r="A21" s="143">
+      <c r="A21" s="112">
         <v>13</v>
       </c>
-      <c r="B21" s="150" t="s">
+      <c r="B21" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="151" t="s">
+      <c r="C21" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="151"/>
-      <c r="E21" s="152">
+      <c r="D21" s="120"/>
+      <c r="E21" s="121">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="147">
-        <v>1991817.2494090125</v>
-      </c>
-      <c r="G21" s="178">
-        <v>0</v>
-      </c>
-      <c r="H21" s="148">
+      <c r="F21" s="116">
+        <v>2161953.9345871457</v>
+      </c>
+      <c r="G21" s="135">
+        <v>0</v>
+      </c>
+      <c r="H21" s="117">
         <f t="shared" si="0"/>
-        <v>1991817.2494090125</v>
-      </c>
-      <c r="I21" s="148">
+        <v>2161953.9345871457</v>
+      </c>
+      <c r="I21" s="117">
         <f t="shared" si="7"/>
-        <v>73697.238228133472</v>
-      </c>
-      <c r="J21" s="148">
+        <v>79992.295579724407</v>
+      </c>
+      <c r="J21" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="148">
+      <c r="K21" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="148">
+        <v>4235</v>
+      </c>
+      <c r="L21" s="117">
         <f t="shared" si="3"/>
-        <v>21964.634999999998</v>
-      </c>
-      <c r="M21" s="149">
+        <v>38391.943975000002</v>
+      </c>
+      <c r="M21" s="118">
         <f t="shared" si="4"/>
         <v>74474.811950000003</v>
       </c>
-      <c r="N21" s="149">
+      <c r="N21" s="118">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O21" s="184">
+      <c r="O21" s="140">
         <f t="shared" si="6"/>
-        <v>2161953.9345871457</v>
-      </c>
-      <c r="Q21" s="180"/>
+        <v>2359047.9860918703</v>
+      </c>
+      <c r="Q21" s="136"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1">
-      <c r="A22" s="51">
+      <c r="A22" s="48">
         <v>14</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="93" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="47">
+      <c r="D22" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="44">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F22" s="17">
-        <v>157274.03213399998</v>
-      </c>
-      <c r="G22" s="176">
-        <f>F22</f>
-        <v>157274.03213399998</v>
-      </c>
-      <c r="H22" s="24">
+      <c r="F22" s="14">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="G22" s="133">
+        <f>F22+RESUMEN!H43</f>
+        <v>212626.65312999999</v>
+      </c>
+      <c r="H22" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="68">
+        <v>122700</v>
+      </c>
+      <c r="K22" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="68">
+        <v>3949</v>
+      </c>
+      <c r="L22" s="62">
         <f t="shared" si="3"/>
-        <v>20481.309000000001</v>
-      </c>
-      <c r="M22" s="25">
+        <v>35799.241264999997</v>
+      </c>
+      <c r="M22" s="22">
         <f t="shared" si="4"/>
         <v>69445.344129999998</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="183">
+      <c r="O22" s="139">
         <f t="shared" si="6"/>
-        <v>89926.653129999992</v>
-      </c>
-      <c r="Q22" s="180"/>
+        <v>-13506.414605000005</v>
+      </c>
+      <c r="Q22" s="136"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1">
-      <c r="A23" s="51">
+      <c r="A23" s="48">
         <v>15</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="48">
+      <c r="D23" s="80" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F23" s="17">
-        <v>181368.73672799996</v>
-      </c>
-      <c r="G23" s="176">
+      <c r="F23" s="14">
+        <v>103703.71698</v>
+      </c>
+      <c r="G23" s="133">
         <f>F23</f>
-        <v>181368.73672799996</v>
-      </c>
-      <c r="H23" s="24">
+        <v>103703.71698</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J23" s="24">
+      <c r="J23" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="68">
+      <c r="K23" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="68">
+        <v>4554</v>
+      </c>
+      <c r="L23" s="62">
         <f t="shared" si="3"/>
-        <v>23619.114000000001</v>
-      </c>
-      <c r="M23" s="25">
+        <v>41283.804689999997</v>
+      </c>
+      <c r="M23" s="22">
         <f t="shared" si="4"/>
         <v>80084.602979999996</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O23" s="183">
+      <c r="O23" s="139">
         <f t="shared" si="6"/>
-        <v>103703.71698</v>
-      </c>
-      <c r="Q23" s="180"/>
+        <v>125922.40766999999</v>
+      </c>
+      <c r="Q23" s="136"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1">
-      <c r="A24" s="51">
+      <c r="A24" s="48">
         <v>16</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="95" t="s">
+      <c r="C24" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="49">
+      <c r="D24" s="81"/>
+      <c r="E24" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F24" s="17">
-        <v>234377.73590999999</v>
-      </c>
-      <c r="G24" s="176">
+      <c r="F24" s="14">
+        <v>134013.25745</v>
+      </c>
+      <c r="G24" s="133">
         <f>F24</f>
-        <v>234377.73590999999</v>
-      </c>
-      <c r="H24" s="24">
+        <v>134013.25745</v>
+      </c>
+      <c r="H24" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="68">
+      <c r="K24" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="68">
+        <v>5885</v>
+      </c>
+      <c r="L24" s="62">
         <f t="shared" si="3"/>
-        <v>30522.285</v>
-      </c>
-      <c r="M24" s="25">
+        <v>53349.844225000001</v>
+      </c>
+      <c r="M24" s="22">
         <f t="shared" si="4"/>
         <v>103490.97245</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O24" s="183">
+      <c r="O24" s="139">
         <f t="shared" si="6"/>
-        <v>134013.25745</v>
-      </c>
-      <c r="Q24" s="180"/>
+        <v>162725.81667500001</v>
+      </c>
+      <c r="Q24" s="136"/>
     </row>
     <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A25" s="51">
+      <c r="A25" s="48">
         <v>17</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="95" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" s="49">
+      <c r="C25" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="46">
         <v>3.85E-2</v>
       </c>
-      <c r="F25" s="17">
-        <v>168663.88801999995</v>
-      </c>
-      <c r="G25" s="176">
+      <c r="F25" s="14">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="G25" s="133">
         <f>F25</f>
-        <v>168663.88801999995</v>
-      </c>
-      <c r="H25" s="24">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J25" s="24">
+      <c r="J25" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="68">
+      <c r="K25" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="68">
+        <v>4235</v>
+      </c>
+      <c r="L25" s="62">
         <f t="shared" si="3"/>
-        <v>21964.634999999998</v>
-      </c>
-      <c r="M25" s="25">
+        <v>38391.943975000002</v>
+      </c>
+      <c r="M25" s="22">
         <f t="shared" si="4"/>
         <v>74474.811950000003</v>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O25" s="183">
+      <c r="O25" s="139">
         <f t="shared" si="6"/>
-        <v>96439.446949999998</v>
-      </c>
-      <c r="Q25" s="181"/>
+        <v>117101.755925</v>
+      </c>
+      <c r="Q25" s="137"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1">
-      <c r="A26" s="51">
+      <c r="A26" s="48">
         <v>18</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="95"/>
-      <c r="E26" s="49">
+      <c r="D26" s="81"/>
+      <c r="E26" s="46">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F26" s="17">
-        <v>157274.03213399998</v>
-      </c>
-      <c r="G26" s="176">
+      <c r="F26" s="14">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="G26" s="133">
         <f>F26</f>
-        <v>157274.03213399998</v>
-      </c>
-      <c r="H26" s="24">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="H26" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J26" s="24">
+      <c r="J26" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="68">
+      <c r="K26" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="68">
+        <v>3949</v>
+      </c>
+      <c r="L26" s="62">
         <f t="shared" si="3"/>
-        <v>20481.309000000001</v>
-      </c>
-      <c r="M26" s="25">
+        <v>35799.241264999997</v>
+      </c>
+      <c r="M26" s="22">
         <f t="shared" si="4"/>
         <v>69445.344129999998</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O26" s="183">
+      <c r="O26" s="139">
         <f t="shared" si="6"/>
-        <v>89926.653129999992</v>
-      </c>
-      <c r="Q26" s="180"/>
+        <v>109193.585395</v>
+      </c>
+      <c r="Q26" s="136"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1">
-      <c r="A27" s="143">
+      <c r="A27" s="112">
         <v>19</v>
       </c>
-      <c r="B27" s="144" t="s">
+      <c r="B27" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="145" t="s">
+      <c r="C27" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="146">
+      <c r="D27" s="114" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="115">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="147">
-        <v>3724071.6003557066</v>
-      </c>
-      <c r="G27" s="177">
-        <v>181369.14</v>
-      </c>
-      <c r="H27" s="170">
+      <c r="F27" s="116">
+        <v>3777486.1683688676</v>
+      </c>
+      <c r="G27" s="134">
+        <v>103703.6</v>
+      </c>
+      <c r="H27" s="131">
         <f t="shared" si="0"/>
-        <v>3542702.4603557065</v>
-      </c>
-      <c r="I27" s="148">
+        <v>3673782.5683688675</v>
+      </c>
+      <c r="I27" s="117">
         <f t="shared" si="7"/>
-        <v>131079.99103316115</v>
-      </c>
-      <c r="J27" s="148">
+        <v>135929.95502964812</v>
+      </c>
+      <c r="J27" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="148">
+      <c r="K27" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="148">
+        <v>4554</v>
+      </c>
+      <c r="L27" s="117">
         <f t="shared" si="3"/>
-        <v>23619.114000000001</v>
-      </c>
-      <c r="M27" s="149">
+        <v>41283.804689999997</v>
+      </c>
+      <c r="M27" s="118">
         <f t="shared" si="4"/>
         <v>80084.602979999996</v>
       </c>
-      <c r="N27" s="149">
+      <c r="N27" s="118">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O27" s="184">
+      <c r="O27" s="140">
         <f t="shared" si="6"/>
-        <v>3777486.1683688676</v>
-      </c>
-      <c r="P27" s="182">
+        <v>3935634.9310685159</v>
+      </c>
+      <c r="P27" s="138">
         <f>M27+N27</f>
         <v>80084.602979999996</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A28" s="51">
+      <c r="A28" s="48">
         <v>20</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="95" t="s">
+      <c r="C28" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="95"/>
-      <c r="E28" s="49">
+      <c r="D28" s="81"/>
+      <c r="E28" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F28" s="17">
-        <v>3388884.5704627023</v>
-      </c>
-      <c r="G28" s="176"/>
-      <c r="H28" s="68">
+      <c r="F28" s="14">
+        <v>3648286.5570198223</v>
+      </c>
+      <c r="G28" s="133"/>
+      <c r="H28" s="62">
         <f t="shared" si="0"/>
-        <v>3388884.5704627023</v>
-      </c>
-      <c r="I28" s="24">
+        <v>3648286.5570198223</v>
+      </c>
+      <c r="I28" s="21">
         <f t="shared" si="7"/>
-        <v>125388.72910712</v>
-      </c>
-      <c r="J28" s="24">
+        <v>134986.60260973344</v>
+      </c>
+      <c r="J28" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="68">
+      <c r="K28" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="68">
+        <v>5885</v>
+      </c>
+      <c r="L28" s="62">
         <f t="shared" si="3"/>
-        <v>30522.285</v>
-      </c>
-      <c r="M28" s="25">
+        <v>53349.844225000001</v>
+      </c>
+      <c r="M28" s="22">
         <f t="shared" si="4"/>
         <v>103490.97245</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O28" s="183">
+      <c r="O28" s="139">
         <f t="shared" si="6"/>
-        <v>3648286.5570198223</v>
+        <v>3945998.9763045558</v>
       </c>
       <c r="P28" s="7"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1">
-      <c r="A29" s="51">
+      <c r="A29" s="48">
         <v>21</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="95"/>
-      <c r="E29" s="49">
+      <c r="C29" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="46">
         <v>3.85E-2</v>
       </c>
-      <c r="F29" s="17">
-        <v>168664.35200999997</v>
-      </c>
-      <c r="G29" s="176">
+      <c r="F29" s="14">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="G29" s="133">
         <f>F29</f>
-        <v>168664.35200999997</v>
-      </c>
-      <c r="H29" s="24">
+        <v>96439.446949999998</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J29" s="24">
+      <c r="J29" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="68">
+      <c r="K29" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="68">
+        <v>4235</v>
+      </c>
+      <c r="L29" s="62">
         <f t="shared" si="3"/>
-        <v>21964.634999999998</v>
-      </c>
-      <c r="M29" s="25">
+        <v>38391.943975000002</v>
+      </c>
+      <c r="M29" s="22">
         <f t="shared" si="4"/>
         <v>74474.811950000003</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O29" s="183">
+      <c r="O29" s="139">
         <f t="shared" si="6"/>
-        <v>96439.446949999998</v>
+        <v>117101.755925</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
@@ -4946,284 +5225,284 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
-      <c r="A30" s="51">
+      <c r="A30" s="48">
         <v>22</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="95" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="95" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" s="49">
+      <c r="C30" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="46">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F30" s="17">
-        <v>157274.03213399998</v>
-      </c>
-      <c r="G30" s="176">
+      <c r="F30" s="14">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="G30" s="133">
         <f>F30</f>
-        <v>157274.03213399998</v>
-      </c>
-      <c r="H30" s="24">
+        <v>89926.653129999992</v>
+      </c>
+      <c r="H30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="68">
+      <c r="K30" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="68">
+        <v>3949</v>
+      </c>
+      <c r="L30" s="62">
         <f t="shared" si="3"/>
-        <v>20481.309000000001</v>
-      </c>
-      <c r="M30" s="25">
+        <v>35799.241264999997</v>
+      </c>
+      <c r="M30" s="22">
         <f t="shared" si="4"/>
         <v>69445.344129999998</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O30" s="183">
+      <c r="O30" s="139">
         <f t="shared" si="6"/>
-        <v>89926.653129999992</v>
+        <v>109193.585395</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
-      <c r="A31" s="51">
+      <c r="A31" s="48">
         <v>23</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="95" t="s">
+      <c r="C31" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="95"/>
-      <c r="E31" s="49">
+      <c r="D31" s="81"/>
+      <c r="E31" s="46">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F31" s="17">
-        <v>175829.73672799996</v>
-      </c>
-      <c r="G31" s="176">
+      <c r="F31" s="14">
+        <v>103703.71698</v>
+      </c>
+      <c r="G31" s="133">
         <f>F31</f>
-        <v>175829.73672799996</v>
-      </c>
-      <c r="H31" s="24">
+        <v>103703.71698</v>
+      </c>
+      <c r="H31" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J31" s="24">
+      <c r="J31" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K31" s="68">
+      <c r="K31" s="62">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="68">
+        <v>4554</v>
+      </c>
+      <c r="L31" s="62">
         <f t="shared" si="3"/>
-        <v>23619.114000000001</v>
-      </c>
-      <c r="M31" s="25">
+        <v>41283.804689999997</v>
+      </c>
+      <c r="M31" s="22">
         <f t="shared" si="4"/>
         <v>80084.602979999996</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O31" s="183">
+      <c r="O31" s="139">
         <f t="shared" si="6"/>
-        <v>103703.71698</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
-      <c r="A32" s="37"/>
-      <c r="B32" s="52">
+        <v>125922.40766999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
+      <c r="A32" s="34"/>
+      <c r="B32" s="49">
         <f>SUM(B9:B31)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="53">
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="50">
         <f>SUM(E9:E31)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="99">
+      <c r="F32" s="85">
         <f>SUM(F9:F31)</f>
-        <v>22743146.39998062</v>
-      </c>
-      <c r="G32" s="99">
+        <v>22272713.974063884</v>
+      </c>
+      <c r="G32" s="85">
         <f>SUM(G9:G31)</f>
-        <v>3698920.7905269074</v>
-      </c>
-      <c r="H32" s="122">
+        <v>2157075.7076916099</v>
+      </c>
+      <c r="H32" s="107">
         <f>SUM(H9:H31)</f>
-        <v>19304531.4759508</v>
-      </c>
-      <c r="I32" s="54">
+        <v>20399417.479739368</v>
+      </c>
+      <c r="I32" s="51">
         <f>SUM(I9:I31)</f>
-        <v>714267.66461017949</v>
-      </c>
-      <c r="J32" s="99">
+        <v>754778.4467503567</v>
+      </c>
+      <c r="J32" s="85">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>260305.86649708962</v>
-      </c>
-      <c r="K32" s="90">
+        <v>283779.21336708963</v>
+      </c>
+      <c r="K32" s="76">
         <f>SUM(K9:K31)</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="90"/>
-      <c r="M32" s="54">
+        <v>110000</v>
+      </c>
+      <c r="L32" s="76"/>
+      <c r="M32" s="51">
         <f>SUM(M9:M31)</f>
         <v>1934410.7000000002</v>
       </c>
-      <c r="N32" s="90">
+      <c r="N32" s="76">
         <f>SUM(N9:N31)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="54">
+      <c r="O32" s="51">
         <f>SUM(O9:O31)</f>
-        <v>22263413.974063884</v>
+        <v>23912020.763122637</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="229"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="229"/>
-      <c r="J34" s="229"/>
-      <c r="K34" s="229"/>
-      <c r="L34" s="229"/>
-      <c r="M34" s="229"/>
-      <c r="N34" s="229"/>
-      <c r="O34" s="229"/>
+      <c r="B34" s="151"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="151"/>
+      <c r="E34" s="151"/>
+      <c r="F34" s="151"/>
+      <c r="G34" s="151"/>
+      <c r="H34" s="151"/>
+      <c r="I34" s="151"/>
+      <c r="J34" s="151"/>
+      <c r="K34" s="151"/>
+      <c r="L34" s="151"/>
+      <c r="M34" s="151"/>
+      <c r="N34" s="151"/>
+      <c r="O34" s="151"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="229"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="229"/>
-      <c r="O35" s="229"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="151"/>
+      <c r="H35" s="151"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="151"/>
+      <c r="K35" s="151"/>
+      <c r="L35" s="151"/>
+      <c r="M35" s="151"/>
+      <c r="N35" s="151"/>
+      <c r="O35" s="151"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="229"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="229"/>
+      <c r="B36" s="151"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="151"/>
+      <c r="H36" s="151"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="151"/>
+      <c r="K36" s="151"/>
+      <c r="L36" s="151"/>
+      <c r="M36" s="151"/>
+      <c r="N36" s="151"/>
+      <c r="O36" s="151"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="229"/>
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="229"/>
-      <c r="J37" s="229"/>
-      <c r="K37" s="229"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="229"/>
-      <c r="N37" s="229"/>
-      <c r="O37" s="229"/>
+      <c r="B37" s="151"/>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="151"/>
+      <c r="H37" s="151"/>
+      <c r="I37" s="151"/>
+      <c r="J37" s="151"/>
+      <c r="K37" s="151"/>
+      <c r="L37" s="151"/>
+      <c r="M37" s="151"/>
+      <c r="N37" s="151"/>
+      <c r="O37" s="151"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="231"/>
-      <c r="B38" s="231"/>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="231"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="231"/>
-      <c r="N38" s="231"/>
-      <c r="O38" s="231"/>
+      <c r="A38" s="153"/>
+      <c r="B38" s="153"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="153"/>
+      <c r="G38" s="153"/>
+      <c r="H38" s="153"/>
+      <c r="I38" s="153"/>
+      <c r="J38" s="153"/>
+      <c r="K38" s="153"/>
+      <c r="L38" s="153"/>
+      <c r="M38" s="153"/>
+      <c r="N38" s="153"/>
+      <c r="O38" s="153"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="231"/>
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="231"/>
-      <c r="N39" s="231"/>
-      <c r="O39" s="231"/>
+      <c r="A39" s="153"/>
+      <c r="B39" s="153"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="153"/>
+      <c r="H39" s="153"/>
+      <c r="I39" s="153"/>
+      <c r="J39" s="153"/>
+      <c r="K39" s="153"/>
+      <c r="L39" s="153"/>
+      <c r="M39" s="153"/>
+      <c r="N39" s="153"/>
+      <c r="O39" s="153"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="231"/>
-      <c r="B40" s="231"/>
-      <c r="C40" s="231"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="231"/>
-      <c r="O40" s="231"/>
+      <c r="A40" s="153"/>
+      <c r="B40" s="153"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="153"/>
+      <c r="H40" s="153"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="153"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="153"/>
+      <c r="M40" s="153"/>
+      <c r="N40" s="153"/>
+      <c r="O40" s="153"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5248,631 +5527,631 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="238" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="240"/>
+      <c r="A1" s="160" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="162"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="30"/>
-      <c r="G2" s="31"/>
+      <c r="A2" s="27"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="57"/>
-      <c r="B3" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="31"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="58"/>
-      <c r="B4" s="63">
+      <c r="A4" s="53"/>
+      <c r="B4" s="57">
         <v>400000</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="G4" s="31"/>
+      <c r="D4" s="11"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="62"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="67">
+      <c r="A5" s="56"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="61">
         <v>9508.5</v>
       </c>
-      <c r="G5" s="31"/>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="72"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="16"/>
-      <c r="G6" s="31"/>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="16"/>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
-      <c r="A8" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="27" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="13"/>
+      <c r="G6" s="28"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A7" s="56"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="13"/>
+      <c r="G7" s="28"/>
+    </row>
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
+      <c r="A8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="29" t="s">
+      <c r="F8" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="50">
+      <c r="A9" s="47">
         <v>1</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="42">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="E9" s="70">
+      <c r="E9" s="63">
         <f>B$4*D9</f>
         <v>16200</v>
       </c>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70" t="s">
-        <v>96</v>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="51">
+      <c r="A10" s="48">
         <v>2</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="42">
         <v>6.4799999999999996E-2</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="63">
         <f t="shared" ref="E10:E31" si="0">B$4*D10</f>
         <v>25920</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70" t="s">
-        <v>96</v>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="51">
+      <c r="A11" s="48">
         <v>3</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>4.82E-2</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="63">
         <f t="shared" si="0"/>
         <v>19280</v>
       </c>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70" t="s">
-        <v>96</v>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="51">
+      <c r="A12" s="48">
         <v>4</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="42">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="63">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70" t="s">
-        <v>96</v>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="51">
+      <c r="A13" s="48">
         <v>5</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="42">
         <v>3.85E-2</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="63">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70" t="s">
-        <v>96</v>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="51">
+      <c r="A14" s="48">
         <v>6</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="42">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="63">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F14" s="70">
+      <c r="F14" s="63">
         <f>E14*6.3%</f>
         <v>904.68</v>
       </c>
-      <c r="G14" s="70">
+      <c r="G14" s="63">
         <f t="shared" ref="G14:G27" si="1">E14 +F14</f>
         <v>15264.68</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="51">
+      <c r="A15" s="48">
         <v>7</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="42">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="63">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70" t="s">
-        <v>96</v>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="51">
+      <c r="A16" s="48">
         <v>8</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="42">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="63">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70" t="s">
-        <v>96</v>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="51">
+      <c r="A17" s="48">
         <v>9</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="42">
         <v>3.85E-2</v>
       </c>
-      <c r="E17" s="70">
+      <c r="E17" s="63">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70" t="s">
-        <v>96</v>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="51">
+      <c r="A18" s="48">
         <v>10</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="42">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="63">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70" t="s">
-        <v>96</v>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="51">
+      <c r="A19" s="48">
         <v>11</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="42">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="63">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="63">
         <f>E19*6.3%</f>
         <v>1043.28</v>
       </c>
-      <c r="G19" s="70">
+      <c r="G19" s="63">
         <f t="shared" si="1"/>
         <v>17603.28</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="51">
+      <c r="A20" s="48">
         <v>12</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="43">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="63">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70" t="s">
-        <v>96</v>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="51">
+      <c r="A21" s="48">
         <v>13</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="44">
         <v>3.85E-2</v>
       </c>
-      <c r="E21" s="70">
+      <c r="E21" s="63">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70" t="s">
-        <v>96</v>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="51">
+      <c r="A22" s="48">
         <v>14</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="44">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E22" s="70">
+      <c r="E22" s="63">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70" t="s">
-        <v>96</v>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="51">
+      <c r="A23" s="48">
         <v>15</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="63">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.6">
-      <c r="A24" s="51">
+      <c r="F23" s="63"/>
+      <c r="G23" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75">
+      <c r="A24" s="48">
         <v>16</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="65" t="s">
+      <c r="C24" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="49">
+      <c r="D24" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E24" s="70">
+      <c r="E24" s="63">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.6">
-      <c r="A25" s="51">
+      <c r="F24" s="63"/>
+      <c r="G24" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75">
+      <c r="A25" s="48">
         <v>17</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="49">
+      <c r="C25" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="46">
         <v>3.85E-2</v>
       </c>
-      <c r="E25" s="70">
+      <c r="E25" s="63">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.6">
-      <c r="A26" s="51">
+      <c r="F25" s="63"/>
+      <c r="G25" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75">
+      <c r="A26" s="48">
         <v>18</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="49">
+      <c r="D26" s="46">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="63">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.6">
-      <c r="A27" s="51">
+      <c r="F26" s="63"/>
+      <c r="G26" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75">
+      <c r="A27" s="48">
         <v>19</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="49">
+      <c r="D27" s="46">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E27" s="63">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F27" s="70">
+      <c r="F27" s="63">
         <f>E27*6.3%</f>
         <v>1043.28</v>
       </c>
-      <c r="G27" s="70">
+      <c r="G27" s="63">
         <f t="shared" si="1"/>
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
-      <c r="A28" s="51">
+    <row r="28" spans="1:7" ht="15.75">
+      <c r="A28" s="48">
         <v>20</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="49">
+      <c r="D28" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E28" s="70">
+      <c r="E28" s="63">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.6">
-      <c r="A29" s="51">
+      <c r="F28" s="63"/>
+      <c r="G28" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75">
+      <c r="A29" s="48">
         <v>21</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="65" t="s">
+      <c r="C29" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="49">
+      <c r="D29" s="46">
         <v>3.85E-2</v>
       </c>
-      <c r="E29" s="70">
+      <c r="E29" s="63">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.6">
-      <c r="A30" s="51">
+      <c r="F29" s="63"/>
+      <c r="G29" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75">
+      <c r="A30" s="48">
         <v>22</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="C30" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="46">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="E30" s="70">
+      <c r="E30" s="63">
         <f t="shared" si="0"/>
         <v>14360</v>
       </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.6">
-      <c r="A31" s="51">
+      <c r="F30" s="63"/>
+      <c r="G30" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75">
+      <c r="A31" s="48">
         <v>23</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="65" t="s">
+      <c r="C31" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="46">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E31" s="70">
+      <c r="E31" s="63">
         <f t="shared" si="0"/>
         <v>16560</v>
       </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.6">
-      <c r="A32" s="37"/>
-      <c r="B32" s="52">
+      <c r="F31" s="63"/>
+      <c r="G31" s="63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75">
+      <c r="A32" s="34"/>
+      <c r="B32" s="49">
         <f>SUM(B9:B31)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="53">
+      <c r="C32" s="34"/>
+      <c r="D32" s="50">
         <f>SUM(D9:D31)</f>
         <v>1</v>
       </c>
-      <c r="E32" s="54">
+      <c r="E32" s="51">
         <f>SUM(E9:E31)</f>
         <v>400000</v>
       </c>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
     </row>
     <row r="34" spans="3:5" ht="13.5" customHeight="1">
-      <c r="C34" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="75"/>
-      <c r="E34" s="76">
+      <c r="C34" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="67"/>
+      <c r="E34" s="68">
         <f>SUMIF(G9:G31,"pago",E9:E31)</f>
         <v>352520</v>
       </c>
